--- a/SHB01D.xlsx
+++ b/SHB01D.xlsx
@@ -235,7 +235,7 @@
     <t>20142232</t>
   </si>
   <si>
-    <t>IDM POPCRN CHOCO 65G</t>
+    <t>IDM POPCRN CHOC 65 G</t>
   </si>
   <si>
     <t>20134686</t>
@@ -265,7 +265,7 @@
     <t>20052766</t>
   </si>
   <si>
-    <t>IDM KCNG METE MDU 80</t>
+    <t>IDM KCNG METE MDU 65</t>
   </si>
   <si>
     <t>20126521</t>
@@ -277,7 +277,7 @@
     <t>20097515</t>
   </si>
   <si>
-    <t>IDM POP CORN CRML 75</t>
+    <t>IDM POPCRN CRML 75 G</t>
   </si>
   <si>
     <t>8</t>
@@ -286,7 +286,7 @@
     <t>20102071</t>
   </si>
   <si>
-    <t>IDM POPCRN SW.CHS 65</t>
+    <t>IDM POPCRN S.CH 65 G</t>
   </si>
   <si>
     <t>9</t>

--- a/SHB01D.xlsx
+++ b/SHB01D.xlsx
@@ -163,13 +163,13 @@
     <t>20072230</t>
   </si>
   <si>
-    <t>IDM KCNG KORO ORG140</t>
+    <t>IDM K KORO ORI 140 G</t>
   </si>
   <si>
     <t>20087344</t>
   </si>
   <si>
-    <t>IDM KCG KORO KLT 170</t>
+    <t>IDM K KORO KLT 170 G</t>
   </si>
   <si>
     <t>20089256</t>
@@ -259,7 +259,7 @@
     <t>20096682</t>
   </si>
   <si>
-    <t>IDM KACANG JUMBO 80</t>
+    <t>IDM K JUMBO 80 G</t>
   </si>
   <si>
     <t>20052766</t>

--- a/SHB01D.xlsx
+++ b/SHB01D.xlsx
@@ -247,13 +247,13 @@
     <t>20128291</t>
   </si>
   <si>
-    <t>IDM KCG ALMD MADU 65</t>
+    <t>IDM KCG ALMD MD 65 G</t>
   </si>
   <si>
     <t>20104000</t>
   </si>
   <si>
-    <t>IDM KACANG ALMOND 65</t>
+    <t>IDM KCG ALMD 65 G</t>
   </si>
   <si>
     <t>20096682</t>
